--- a/data/trans_dic/IP31KM01_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM01_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>92,67; 99,31</t>
+          <t>87,73; 98,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>90,23; 98,58</t>
+          <t>90,86; 99,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92,81; 98,55</t>
+          <t>91,14; 98,01</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>80,91%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>78,77; 93,97</t>
+          <t>72,75; 86,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>72,57; 85,84</t>
+          <t>75,04; 88,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77,89; 88,12</t>
+          <t>75,94; 85,49</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,79%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>83,13; 95,71</t>
+          <t>85,76; 96,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,12; 96,45</t>
+          <t>82,08; 95,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86,47; 95,01</t>
+          <t>86,79; 95,22</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,33%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>82,97; 95,92</t>
+          <t>66,45; 89,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69,48; 91,24</t>
+          <t>84,75; 96,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,06; 91,53</t>
+          <t>78,68; 91,6</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>91,76; 100,0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>96,18; 100,0</t>
+          <t>96,22; 100,0</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,03%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>75,31; 92,06</t>
+          <t>89,76; 99,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>90,76; 99,18</t>
+          <t>74,71; 91,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86,45; 95,23</t>
+          <t>85,25; 94,7</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,85%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>78,99; 90,04</t>
+          <t>76,9; 88,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>71,15; 88,25</t>
+          <t>78,57; 89,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>76,4; 87,31</t>
+          <t>79,29; 87,9</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>96,42; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>96,49; 100,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>98,34; 100,0</t>
+          <t>98,17; 100,0</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,29%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>88,95; 92,91</t>
+          <t>87,51; 91,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>86,8; 91,59</t>
+          <t>88,58; 92,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>88,57; 91,71</t>
+          <t>88,84; 91,77</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>69450</t>
+          <t>57210</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>71410</t>
+          <t>53073</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>140861</t>
+          <t>110284</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>66167; 70904</t>
+          <t>52869; 59560</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>67317; 73544</t>
+          <t>49904; 54413</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>135514; 143892</t>
+          <t>104984; 112890</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>114</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>107979</t>
+          <t>91695</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>101080</t>
+          <t>81678</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>209058</t>
+          <t>173374</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>98978; 118073</t>
+          <t>83627; 99469</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>91745; 108523</t>
+          <t>74541; 87502</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>196351; 222126</t>
+          <t>162734; 183198</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>83</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>50591</t>
+          <t>53032</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>59576</t>
+          <t>49234</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>110167</t>
+          <t>102266</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>46182; 53170</t>
+          <t>49138; 55327</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>55012; 62339</t>
+          <t>44413; 51713</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>103923; 114191</t>
+          <t>96688; 106089</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>85</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>63441</t>
+          <t>56255</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>61567</t>
+          <t>64840</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>125009</t>
+          <t>121095</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>57816; 66836</t>
+          <t>46394; 62705</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52362; 68769</t>
+          <t>59717; 67980</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>114673; 132768</t>
+          <t>110373; 128497</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>66</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>33647</t>
+          <t>39579</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>34818</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74366</t>
+          <t>74397</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>31381; 34200</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>32456; 35370</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>72058; 74919</t>
+          <t>72113; 74949</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>63</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>37798</t>
+          <t>45681</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>52015</t>
+          <t>37605</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>89813</t>
+          <t>83286</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>33354; 40773</t>
+          <t>42374; 46906</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>48811; 53342</t>
+          <t>33085; 40718</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>84787; 93393</t>
+          <t>78002; 86649</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>149</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>105673</t>
+          <t>116978</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>126799</t>
+          <t>103035</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>232472</t>
+          <t>220014</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>97705; 111374</t>
+          <t>108104; 124827</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>110307; 136826</t>
+          <t>95710; 109453</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>212944; 243374</t>
+          <t>208046; 230648</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>182</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>127271</t>
+          <t>157136</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>136487</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>281429</t>
+          <t>293623</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>124063; 128665</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>133058; 137900</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>278126; 282823</t>
+          <t>289650; 295036</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>853</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>831</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>853</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>595849</t>
+          <t>617565</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>667324</t>
+          <t>560772</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1263174</t>
+          <t>1178336</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>580984; 606819</t>
+          <t>601064; 631556</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>646433; 682126</t>
+          <t>547624; 572223</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1238024; 1281985</t>
+          <t>1159390; 1197619</t>
         </is>
       </c>
     </row>
